--- a/apps/isomorphic/public/templates/Vendor_Quote_Template.xlsx
+++ b/apps/isomorphic/public/templates/Vendor_Quote_Template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>JOB DETAILS</t>
   </si>
@@ -53,6 +53,12 @@
     <t>30/03/2026</t>
   </si>
   <si>
+    <t>Master Division</t>
+  </si>
+  <si>
+    <t>WHI</t>
+  </si>
+  <si>
     <t>Total Qty</t>
   </si>
   <si>
@@ -68,7 +74,16 @@
     <t>Shrink, BIBO</t>
   </si>
   <si>
-    <t>PRINT SPECIFICATIONS</t>
+    <t>Divisions</t>
+  </si>
+  <si>
+    <t>SAP Code</t>
+  </si>
+  <si>
+    <t>Altis</t>
+  </si>
+  <si>
+    <t>Arron</t>
   </si>
   <si>
     <t>Size</t>
@@ -174,7 +189,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,13 +200,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -644,154 +652,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1138,7 +1149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="21.6666666666667" customWidth="1"/>
@@ -1188,119 +1199,117 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>3000</v>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
         <v>17</v>
+      </c>
+      <c r="B12" s="2">
+        <v>123456</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>21</v>
+      <c r="B13" s="2">
+        <v>123456</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1311,75 +1320,69 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>34</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
@@ -1387,7 +1390,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
@@ -1395,7 +1398,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
@@ -1403,9 +1406,41 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
         <v>1</v>
       </c>
     </row>
